--- a/insurance_agent_forms/017_life_insurance_application_form--insurance_agent_forms.xlsx
+++ b/insurance_agent_forms/017_life_insurance_application_form--insurance_agent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'teacher'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Teacher'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'pilot'}</t>
+          <t>pilot</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Pilot'}</t>
+          <t>Pilot</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'teacher'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Teacher'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'pilot'}</t>
+          <t>pilot</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Pilot'}</t>
+          <t>Pilot</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'teacher'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Teacher'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'pilot'}</t>
+          <t>pilot</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Pilot'}</t>
+          <t>Pilot</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'term_life_insurance'}</t>
+          <t>term_life_insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Term Life Insurance'}</t>
+          <t>Term Life Insurance</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'whole_life_insurance'}</t>
+          <t>whole_life_insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Whole Life Insurance'}</t>
+          <t>Whole Life Insurance</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'universal_life_insurance'}</t>
+          <t>universal_life_insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Universal Life Insurance'}</t>
+          <t>Universal Life Insurance</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'joint'}</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Joint'}</t>
+          <t>Joint</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'joint_with_beneficiary'}</t>
+          <t>joint_with_beneficiary</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Joint with Beneficiary'}</t>
+          <t>Joint with Beneficiary</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'single_life_insurance'}</t>
+          <t>single_life_insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Single Life Insurance'}</t>
+          <t>Single Life Insurance</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'joint_life_insurance'}</t>
+          <t>joint_life_insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Joint Life Insurance'}</t>
+          <t>Joint Life Insurance</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'universal_life_insurance'}</t>
+          <t>universal_life_insurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Universal Life Insurance'}</t>
+          <t>Universal Life Insurance</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'1_year'}</t>
+          <t>1_year</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': '1 year'}</t>
+          <t>1 year</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'5_years'}</t>
+          <t>5_years</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': '5 years'}</t>
+          <t>5 years</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'10_years'}</t>
+          <t>10_years</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': '10 years'}</t>
+          <t>10 years</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'insurance_company'}</t>
+          <t>insurance_company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Insurance Company'}</t>
+          <t>Insurance Company</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'insurance_agent'}</t>
+          <t>insurance_agent</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Insurance Agent'}</t>
+          <t>Insurance Agent</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
